--- a/sample_input.xlsx
+++ b/sample_input.xlsx
@@ -34,7 +34,7 @@
     <t>Boeing</t>
   </si>
   <si>
-    <t>BOEL</t>
+    <t>Boel</t>
   </si>
   <si>
     <t>Tanner</t>
